--- a/data/metadata/template metadata.xlsx
+++ b/data/metadata/template metadata.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20382"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3C8EA07-2010-4261-9C76-8FEB42763DDD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D3502A9-C02C-4A87-A5FF-CBF788994D0B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="13">
   <si>
     <t>template</t>
   </si>
@@ -53,6 +53,12 @@
   </si>
   <si>
     <t>start_month</t>
+  </si>
+  <si>
+    <t>template 202211</t>
+  </si>
+  <si>
+    <t>blank template 202211</t>
   </si>
 </sst>
 </file>
@@ -370,7 +376,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.88671875" bestFit="1" customWidth="1"/>
@@ -459,6 +465,26 @@
         <v>4</v>
       </c>
     </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5">
+        <v>2022</v>
+      </c>
+      <c r="F5">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
